--- a/samples/stock_count/재고실사_구미창고.xlsx
+++ b/samples/stock_count/재고실사_구미창고.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -54,7 +51,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -434,66 +431,89 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item Code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Count Date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UOM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Count Qty</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Book Qty</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Counter</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Item Code</t>
+          <t>CH-6001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>절삭유</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>구미창고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Count Date</t>
+          <t>2026.9.26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UOM</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Count Qty</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Book Qty</t>
-        </is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>282</v>
+      </c>
+      <c r="G2" t="n">
+        <v>281</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Counter</t>
+          <t>최지은</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CH-6001</t>
-        </is>
-      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>절삭유</t>
+          <t>너트 M8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -508,14 +528,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>282</v>
+        <v>226</v>
       </c>
       <c r="G3" t="n">
-        <v>281</v>
+        <v>226</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -524,9 +544,14 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CP-4004</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>너트 M8</t>
+          <t>스프링 와셔 8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -545,10 +570,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="G4" t="n">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -559,12 +584,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CP-4004</t>
+          <t>RM-2002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스프링 와셔 8</t>
+          <t>알루미늄 봉 30Φ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -579,30 +604,30 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>168</v>
+        <v>486</v>
       </c>
       <c r="G5" t="n">
-        <v>168</v>
+        <v>486</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>최지은</t>
+          <t>박민수</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RM-2002</t>
+          <t>CH-6002</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>알루미늄 봉 30Φ</t>
+          <t>방청유</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -612,19 +637,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026.9.26</t>
+          <t>2026.9.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>486</v>
+        <v>124</v>
       </c>
       <c r="G6" t="n">
-        <v>486</v>
+        <v>124</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -635,12 +660,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CH-6002</t>
+          <t>RM-2001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>방청유</t>
+          <t>알루미늄 봉 20Φ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -650,35 +675,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026.9.31</t>
+          <t>2026.9.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>124</v>
+        <v>353</v>
       </c>
       <c r="G7" t="n">
-        <v>124</v>
+        <v>352</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>박민수</t>
+          <t>최지은</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RM-2001</t>
+          <t>CP-4005</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>알루미늄 봉 20Φ</t>
+          <t>리벳 4mm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -693,14 +718,14 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="G8" t="n">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -711,12 +736,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CP-4005</t>
+          <t>AS-5002</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>리벳 4mm</t>
+          <t>센서 모듈</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,30 +756,30 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>370</v>
+        <v>-3</v>
       </c>
       <c r="G9" t="n">
-        <v>371</v>
+        <v>445</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>최지은</t>
+          <t>박민수</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AS-5002</t>
+          <t>RM-1001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>센서 모듈</t>
+          <t>냉연강판 1.2T</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -769,14 +794,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-3</v>
+        <v>270</v>
       </c>
       <c r="G10" t="n">
-        <v>445</v>
+        <v>270</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -787,12 +812,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RM-1001</t>
+          <t>AS-5001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>냉연강판 1.2T</t>
+          <t>모터 조립체</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -807,30 +832,30 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>270</v>
+        <v>129</v>
       </c>
       <c r="G11" t="n">
-        <v>270</v>
+        <v>130</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>박민수</t>
+          <t>최지은</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AS-5001</t>
+          <t>PK-3003</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>모터 조립체</t>
+          <t>스트레치 필름</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -845,35 +870,35 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>박스</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>129</v>
+        <v>403</v>
       </c>
       <c r="G12" t="n">
-        <v>130</v>
+        <v>403</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>최지은</t>
+          <t>박민수</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PK-3003</t>
+          <t>AS-5004</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>스트레치 필름</t>
+          <t>케이블 하네스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>구미창고</t>
+          <t>평택1창고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -883,54 +908,16 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>박스</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G13" t="n">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="H13" t="inlineStr">
-        <is>
-          <t>박민수</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AS-5004</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>케이블 하네스</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>평택1창고</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026.9.26</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>404</v>
-      </c>
-      <c r="G14" t="n">
-        <v>406</v>
-      </c>
-      <c r="H14" t="inlineStr">
         <is>
           <t>이영희</t>
         </is>
